--- a/data/trans_dic/Predimed_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,83; 24,71</t>
+          <t>17,95; 24,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,5; 24,85</t>
+          <t>19,93; 25,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,5; 23,69</t>
+          <t>19,57; 23,91</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 15,89</t>
+          <t>6,31; 16,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,91; 19,03</t>
+          <t>14,85; 19,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 16,56</t>
+          <t>9,47; 16,65</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 21,12</t>
+          <t>14,38; 21,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 25,85</t>
+          <t>8,35; 25,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 22,08</t>
+          <t>11,11; 21,99</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 20,05</t>
+          <t>14,72; 19,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,11; 21,47</t>
+          <t>14,99; 21,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,94; 19,99</t>
+          <t>15,66; 20,0</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,12; 17,89</t>
+          <t>12,29; 17,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,88; 21,03</t>
+          <t>14,88; 20,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 18,94</t>
+          <t>14,75; 18,82</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia alta a la dieta mediterránea</t>
+          <t>Población con una adherencia alta a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>102825; 142496</t>
+          <t>103494; 144042</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122272; 155798</t>
+          <t>124923; 158584</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>234645; 285088</t>
+          <t>235511; 287739</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65274; 177793</t>
+          <t>70647; 179226</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>132276; 168875</t>
+          <t>131794; 171189</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174950; 332173</t>
+          <t>190065; 333981</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92370; 135693</t>
+          <t>92416; 135660</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>71746; 228981</t>
+          <t>74011; 225219</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161398; 337523</t>
+          <t>169737; 336177</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131233; 178099</t>
+          <t>130758; 175145</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>160405; 227915</t>
+          <t>159139; 228027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310824; 389770</t>
+          <t>305341; 390088</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>390986; 577176</t>
+          <t>396623; 579041</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>515200; 727904</t>
+          <t>515132; 721511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>990921; 1266726</t>
+          <t>986434; 1258894</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R3-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,95; 24,98</t>
+          <t>18,32; 25,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 25,3</t>
+          <t>19,38; 24,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,57; 23,91</t>
+          <t>20,06; 24,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 16,02</t>
+          <t>13,34; 18,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,85; 19,29</t>
+          <t>14,83; 19,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 16,65</t>
+          <t>14,72; 18,05</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 21,11</t>
+          <t>14,41; 20,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 25,42</t>
+          <t>15,57; 20,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,11; 21,99</t>
+          <t>15,86; 19,79</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,72; 19,72</t>
+          <t>14,68; 19,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,99; 21,48</t>
+          <t>17,37; 21,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,66; 20,0</t>
+          <t>16,82; 20,0</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,29; 17,95</t>
+          <t>16,28; 19,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,88; 20,84</t>
+          <t>17,82; 20,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 18,82</t>
+          <t>17,31; 19,3</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>120886</t>
+          <t>134714</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>139475</t>
+          <t>149597</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260361</t>
+          <t>284310</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>103494; 144042</t>
+          <t>114659; 158357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>124923; 158584</t>
+          <t>131275; 168034</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>235511; 287739</t>
+          <t>261454; 317804</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>131485</t>
+          <t>151821</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>149876</t>
+          <t>168365</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>281361</t>
+          <t>320186</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70647; 179226</t>
+          <t>129345; 178553</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>131794; 171189</t>
+          <t>147337; 190147</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>190065; 333981</t>
+          <t>289011; 354317</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>111267</t>
+          <t>127078</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>145998</t>
+          <t>136809</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257265</t>
+          <t>263888</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92416; 135660</t>
+          <t>105130; 150870</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74011; 225219</t>
+          <t>118032; 156973</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169737; 336177</t>
+          <t>235937; 294379</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>152880</t>
+          <t>163862</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>199969</t>
+          <t>209416</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>352849</t>
+          <t>373278</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>130758; 175145</t>
+          <t>139760; 189063</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>159139; 228027</t>
+          <t>188114; 234121</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>305341; 390088</t>
+          <t>342180; 406944</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>516519</t>
+          <t>577475</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>635318</t>
+          <t>664187</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1151836</t>
+          <t>1241662</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>396623; 579041</t>
+          <t>533687; 631365</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>515132; 721511</t>
+          <t>625674; 707948</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>986434; 1258894</t>
+          <t>1175345; 1310511</t>
         </is>
       </c>
     </row>
